--- a/data/preparation/mizuno_pre.xlsx
+++ b/data/preparation/mizuno_pre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/preparation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B055A1A-086B-C242-AA31-F59B3B68FC50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A8D8163-D14E-4B48-BFDB-A96A2EF0BAED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9840" yWindow="600" windowWidth="18960" windowHeight="17400" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" activeTab="4" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
   </bookViews>
   <sheets>
     <sheet name="2021" sheetId="4" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="157">
   <si>
     <t>ID</t>
   </si>
@@ -385,9 +385,6 @@
   </si>
   <si>
     <t>Since its founding in 1906, the Mizuno Group has embraced the corporate philosophy of “Contributing to society through the advancement of sporting goods and the promotion of sports.” This is our core principle, which will not change in the future, and can be said to be Mizuno’s purpose for all stakeholders (raison d’être for the future). In addition, recently, we have also worked on product development with a view to adapting to an aging society and climate change, taking advantage of the knowledge that we have cultivated in sports. For instance, there is still a great difference between healthy life expectancy (the period during which you can live healthily) and life expectancy. We cannot provide medical service to cure disease. However, by providing products that reduce pain and complement lost physical functions, we help people return to as close to a healthy state as possible and offer support for them to live a less inconvenient life. As measures to adapt to climate change, we take on the challenge of resolving various work environment issues, for instance, by providing comfortable apparel, shoes and equipment composed of functional materials and a device to reduce the risk of heatstroke during outdoor work in summer.</t>
-  </si>
-  <si>
-    <t>In 1991,+B8 we launched the Crew 21 Project, a global environment conservation initiative, with the aim of playing the role of a crew member of the Spaceship Earth. Since then, we have actively promoted CSR activities as our corporate social responsibility for 30 years in order to reduce the negative impact of our business activities on the environment and society. We will continue to strengthen our efforts, including developing environmentally friendly products, making effective use of resources, and promoting CSR procurement from suppliers. I believe that sustainability activities, based on responsible corporate behavior associated with business, should not be considered in terms of cost and that these activities will lead to enhancing both our brand value and overall corporate status if we actively promote investment in line with our management strategy.</t>
   </si>
   <si>
     <t>JPN22M07-00</t>
@@ -489,6 +486,36 @@
   </si>
   <si>
     <t>JPN25M06-00</t>
+  </si>
+  <si>
+    <t>neutral</t>
+  </si>
+  <si>
+    <t>STAKE</t>
+  </si>
+  <si>
+    <t>CHALL</t>
+  </si>
+  <si>
+    <t>STRAT</t>
+  </si>
+  <si>
+    <t>MARKET</t>
+  </si>
+  <si>
+    <t>positive</t>
+  </si>
+  <si>
+    <t>PEOPLE</t>
+  </si>
+  <si>
+    <t>In 1991, we launched the Crew 21 Project, a global environment conservation initiative, with the aim of playing the role of a crew member of the Spaceship Earth. Since then, we have actively promoted CSR activities as our corporate social responsibility for 30 years in order to reduce the negative impact of our business activities on the environment and society. We will continue to strengthen our efforts, including developing environmentally friendly products, making effective use of resources, and promoting CSR procurement from suppliers. I believe that sustainability activities, based on responsible corporate behavior associated with business, should not be considered in terms of cost and that these activities will lead to enhancing both our brand value and overall corporate status if we actively promote investment in line with our management strategy.</t>
+  </si>
+  <si>
+    <t>PERF</t>
+  </si>
+  <si>
+    <t>posiitve</t>
   </si>
 </sst>
 </file>
@@ -797,52 +824,52 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:N12" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:N12" totalsRowShown="0" headerRowDxfId="79" dataDxfId="78">
   <autoFilter ref="A1:N12" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="61"/>
-    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="60"/>
-    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="59"/>
-    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="58"/>
-    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="57"/>
-    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="56"/>
-    <tableColumn id="13" xr3:uid="{2A1C2AA7-A09D-9B47-85D8-B0D0F1A70102}" name="Source_type " dataDxfId="55"/>
-    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="54"/>
-    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="53"/>
-    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="52"/>
-    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="51"/>
-    <tableColumn id="14" xr3:uid="{F919392D-BA1E-134A-898B-12A7212DD7BD}" name="Communicator_role" dataDxfId="50"/>
-    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="Communicator_name" dataDxfId="49"/>
-    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="48"/>
+    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="77"/>
+    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="76"/>
+    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="75"/>
+    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="74"/>
+    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="73"/>
+    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="72"/>
+    <tableColumn id="13" xr3:uid="{2A1C2AA7-A09D-9B47-85D8-B0D0F1A70102}" name="Source_type " dataDxfId="71"/>
+    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="70"/>
+    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="69"/>
+    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="68"/>
+    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="67"/>
+    <tableColumn id="14" xr3:uid="{F919392D-BA1E-134A-898B-12A7212DD7BD}" name="Communicator_role" dataDxfId="66"/>
+    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="Communicator_name" dataDxfId="65"/>
+    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="64"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3D8169D6-4FA8-F441-86D0-5D69197E18AC}" name="Tableau134" displayName="Tableau134" ref="A1:N10" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3D8169D6-4FA8-F441-86D0-5D69197E18AC}" name="Tableau134" displayName="Tableau134" ref="A1:N10" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
   <autoFilter ref="A1:N10" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{E0BC4806-A855-DB47-BA1D-14781F79A9CE}" name="ID" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{D845E286-4D69-5042-A131-7571C44429FB}" name="Text" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{37697E80-CBB7-F84B-8723-F48327932846}" name="Text_type" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{D7A298F0-DFAD-FD40-8DAE-537A95A9C5C4}" name="Leadership_context" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{2353F7B0-B4A9-3E43-AF71-62534746786C}" name="Information_valence" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{3396F9A0-A6B8-2C41-B65F-A556C1040BDA}" name="Communication_type" dataDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{3AB741C7-0039-C443-8DF6-19FAF1BFA151}" name="Source_type" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{ADC1FCA5-2AAB-9B4A-BF24-D3FE78F4B7D5}" name="Company" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{2559D739-168D-4645-8196-D85EFBD84AB9}" name="Country" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{60D6637F-757B-8947-967D-940AB81E468E}" name="Year" dataDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{2DBBFDA0-B241-AB4E-9B47-F97CE4F1D854}" name="Covid" dataDxfId="3"/>
-    <tableColumn id="14" xr3:uid="{1550ADF2-C6A4-3248-8F56-636215BDD290}" name="Communicator_role" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{CC2701EA-6CE0-AB48-B69D-24B23F4F854D}" name="Communicator_name" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{B43E31FD-2B7A-FA47-86F7-DDEB9F598002}" name="Comment" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{E0BC4806-A855-DB47-BA1D-14781F79A9CE}" name="ID" dataDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{D845E286-4D69-5042-A131-7571C44429FB}" name="Text" dataDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{37697E80-CBB7-F84B-8723-F48327932846}" name="Text_type" dataDxfId="59"/>
+    <tableColumn id="4" xr3:uid="{D7A298F0-DFAD-FD40-8DAE-537A95A9C5C4}" name="Leadership_context" dataDxfId="58"/>
+    <tableColumn id="5" xr3:uid="{2353F7B0-B4A9-3E43-AF71-62534746786C}" name="Information_valence" dataDxfId="57"/>
+    <tableColumn id="6" xr3:uid="{3396F9A0-A6B8-2C41-B65F-A556C1040BDA}" name="Communication_type" dataDxfId="56"/>
+    <tableColumn id="13" xr3:uid="{3AB741C7-0039-C443-8DF6-19FAF1BFA151}" name="Source_type" dataDxfId="55"/>
+    <tableColumn id="7" xr3:uid="{ADC1FCA5-2AAB-9B4A-BF24-D3FE78F4B7D5}" name="Company" dataDxfId="54"/>
+    <tableColumn id="8" xr3:uid="{2559D739-168D-4645-8196-D85EFBD84AB9}" name="Country" dataDxfId="53"/>
+    <tableColumn id="9" xr3:uid="{60D6637F-757B-8947-967D-940AB81E468E}" name="Year" dataDxfId="52"/>
+    <tableColumn id="10" xr3:uid="{2DBBFDA0-B241-AB4E-9B47-F97CE4F1D854}" name="Covid" dataDxfId="51"/>
+    <tableColumn id="14" xr3:uid="{1550ADF2-C6A4-3248-8F56-636215BDD290}" name="Communicator_role" dataDxfId="50"/>
+    <tableColumn id="11" xr3:uid="{CC2701EA-6CE0-AB48-B69D-24B23F4F854D}" name="Communicator_name" dataDxfId="49"/>
+    <tableColumn id="12" xr3:uid="{B43E31FD-2B7A-FA47-86F7-DDEB9F598002}" name="Comment" dataDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -901,26 +928,26 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{6C9A834F-30DF-2F42-84FD-AAFE0349F91E}" name="Tableau134567" displayName="Tableau134567" ref="A1:N21" totalsRowShown="0" headerRowDxfId="79" dataDxfId="78">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{6C9A834F-30DF-2F42-84FD-AAFE0349F91E}" name="Tableau134567" displayName="Tableau134567" ref="A1:N21" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
   <autoFilter ref="A1:N21" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{650997B9-CC78-E240-834D-86A1818FF143}" name="ID" dataDxfId="77"/>
-    <tableColumn id="2" xr3:uid="{D92CCC64-BA48-CF4F-8AB9-5F521487292D}" name="Text" dataDxfId="76"/>
-    <tableColumn id="3" xr3:uid="{B0DFEB86-6534-4E40-80D3-65597FF9F643}" name="Text_type" dataDxfId="75"/>
-    <tableColumn id="4" xr3:uid="{E5C5873E-736E-A843-94A8-EF0EB0629CB1}" name="Leadership_context" dataDxfId="74"/>
-    <tableColumn id="5" xr3:uid="{91CECF3A-43E8-9B40-A1E0-30B8DAC3D40C}" name="Information_valence" dataDxfId="73"/>
-    <tableColumn id="6" xr3:uid="{EBEBF2BF-D892-1E4E-AC37-3A17592A42A3}" name="Communication_type" dataDxfId="72"/>
-    <tableColumn id="14" xr3:uid="{512DD80A-A73B-ED4B-91E7-E0D7E6E1FC11}" name="Source_type" dataDxfId="71"/>
-    <tableColumn id="7" xr3:uid="{307E0B33-898E-4046-9DE3-295FB09E1955}" name="Company" dataDxfId="70"/>
-    <tableColumn id="8" xr3:uid="{96131E31-CB66-494E-B454-691694ED5837}" name="Country" dataDxfId="69"/>
-    <tableColumn id="9" xr3:uid="{2B04ECCD-FFC0-9641-9D40-37AEE7898021}" name="Year" dataDxfId="68"/>
-    <tableColumn id="10" xr3:uid="{85B3A0E8-C951-6D4A-B205-4D4016B596FB}" name="Covid" dataDxfId="67"/>
-    <tableColumn id="13" xr3:uid="{B626B99D-CA94-0B4B-B6F5-81574D651E06}" name="Communicator_role" dataDxfId="66"/>
-    <tableColumn id="11" xr3:uid="{06E6C654-9080-0F4E-95B8-D495404A2914}" name="Communicator_name" dataDxfId="65"/>
-    <tableColumn id="12" xr3:uid="{F5FFEBDC-8196-474E-A8E1-A74915A2F585}" name="Comment" dataDxfId="64"/>
+    <tableColumn id="1" xr3:uid="{650997B9-CC78-E240-834D-86A1818FF143}" name="ID" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{D92CCC64-BA48-CF4F-8AB9-5F521487292D}" name="Text" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{B0DFEB86-6534-4E40-80D3-65597FF9F643}" name="Text_type" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{E5C5873E-736E-A843-94A8-EF0EB0629CB1}" name="Leadership_context" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{91CECF3A-43E8-9B40-A1E0-30B8DAC3D40C}" name="Information_valence" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{EBEBF2BF-D892-1E4E-AC37-3A17592A42A3}" name="Communication_type" dataDxfId="8"/>
+    <tableColumn id="14" xr3:uid="{512DD80A-A73B-ED4B-91E7-E0D7E6E1FC11}" name="Source_type" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{307E0B33-898E-4046-9DE3-295FB09E1955}" name="Company" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{96131E31-CB66-494E-B454-691694ED5837}" name="Country" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{2B04ECCD-FFC0-9641-9D40-37AEE7898021}" name="Year" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{85B3A0E8-C951-6D4A-B205-4D4016B596FB}" name="Covid" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{B626B99D-CA94-0B4B-B6F5-81574D651E06}" name="Communicator_role" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{06E6C654-9080-0F4E-95B8-D495404A2914}" name="Communicator_name" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{F5FFEBDC-8196-474E-A8E1-A74915A2F585}" name="Comment" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1292,7 +1319,7 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>94</v>
@@ -1311,6 +1338,12 @@
       <c r="C2" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F2" s="1" t="s">
         <v>98</v>
       </c>
@@ -1347,6 +1380,12 @@
       <c r="C3" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F3" s="1" t="s">
         <v>98</v>
       </c>
@@ -1383,6 +1422,12 @@
       <c r="C4" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D4" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F4" s="1" t="s">
         <v>98</v>
       </c>
@@ -1419,6 +1464,12 @@
       <c r="C5" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D5" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F5" s="1" t="s">
         <v>98</v>
       </c>
@@ -1455,6 +1506,12 @@
       <c r="C6" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D6" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F6" s="1" t="s">
         <v>98</v>
       </c>
@@ -1491,6 +1548,12 @@
       <c r="C7" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D7" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F7" s="1" t="s">
         <v>98</v>
       </c>
@@ -1527,6 +1590,12 @@
       <c r="C8" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D8" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F8" s="1" t="s">
         <v>98</v>
       </c>
@@ -1563,6 +1632,12 @@
       <c r="C9" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D9" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F9" s="1" t="s">
         <v>98</v>
       </c>
@@ -1599,6 +1674,12 @@
       <c r="C10" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D10" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F10" s="1" t="s">
         <v>98</v>
       </c>
@@ -1635,6 +1716,12 @@
       <c r="C11" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D11" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>152</v>
+      </c>
       <c r="F11" s="1" t="s">
         <v>98</v>
       </c>
@@ -1663,16 +1750,19 @@
     </row>
     <row r="12" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>142</v>
+      <c r="E12" s="1" t="s">
+        <v>147</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>98</v>
@@ -1761,7 +1851,7 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>94</v>
@@ -1780,6 +1870,12 @@
       <c r="C2" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F2" s="1" t="s">
         <v>96</v>
       </c>
@@ -1815,6 +1911,12 @@
       <c r="C3" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F3" s="1" t="s">
         <v>96</v>
       </c>
@@ -1850,6 +1952,12 @@
       <c r="C4" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D4" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F4" s="1" t="s">
         <v>96</v>
       </c>
@@ -1885,6 +1993,12 @@
       <c r="C5" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D5" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F5" s="1" t="s">
         <v>96</v>
       </c>
@@ -1920,6 +2034,12 @@
       <c r="C6" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D6" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F6" s="1" t="s">
         <v>96</v>
       </c>
@@ -1950,10 +2070,16 @@
         <v>82</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>114</v>
+        <v>154</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>37</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>147</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>96</v>
@@ -1990,6 +2116,12 @@
       <c r="C8" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D8" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>152</v>
+      </c>
       <c r="F8" s="1" t="s">
         <v>96</v>
       </c>
@@ -2017,7 +2149,7 @@
     </row>
     <row r="9" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>77</v>
@@ -2025,6 +2157,12 @@
       <c r="C9" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D9" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F9" s="1" t="s">
         <v>96</v>
       </c>
@@ -2052,16 +2190,19 @@
     </row>
     <row r="10" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>147</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>96</v>
@@ -2149,7 +2290,7 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>94</v>
@@ -2168,6 +2309,12 @@
       <c r="C2" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>152</v>
+      </c>
       <c r="F2" s="1" t="s">
         <v>96</v>
       </c>
@@ -2203,6 +2350,12 @@
       <c r="C3" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>152</v>
+      </c>
       <c r="F3" s="1" t="s">
         <v>96</v>
       </c>
@@ -2238,6 +2391,12 @@
       <c r="C4" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D4" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>152</v>
+      </c>
       <c r="F4" s="1" t="s">
         <v>96</v>
       </c>
@@ -2273,6 +2432,12 @@
       <c r="C5" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D5" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>152</v>
+      </c>
       <c r="F5" s="1" t="s">
         <v>96</v>
       </c>
@@ -2308,6 +2473,12 @@
       <c r="C6" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D6" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F6" s="1" t="s">
         <v>96</v>
       </c>
@@ -2343,6 +2514,12 @@
       <c r="C7" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D7" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F7" s="1" t="s">
         <v>96</v>
       </c>
@@ -2378,6 +2555,12 @@
       <c r="C8" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D8" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F8" s="1" t="s">
         <v>96</v>
       </c>
@@ -2405,7 +2588,7 @@
     </row>
     <row r="9" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>105</v>
@@ -2413,6 +2596,12 @@
       <c r="C9" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D9" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>152</v>
+      </c>
       <c r="F9" s="1" t="s">
         <v>96</v>
       </c>
@@ -2440,16 +2629,19 @@
     </row>
     <row r="10" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>147</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>96</v>
@@ -2537,7 +2729,7 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>94</v>
@@ -2551,11 +2743,17 @@
         <v>17</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F2" s="1" t="s">
         <v>96</v>
       </c>
@@ -2583,14 +2781,20 @@
     </row>
     <row r="3" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F3" s="1" t="s">
         <v>96</v>
       </c>
@@ -2618,13 +2822,19 @@
     </row>
     <row r="4" spans="1:14" ht="255" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>37</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>147</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>96</v>
@@ -2653,14 +2863,20 @@
     </row>
     <row r="5" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="D5" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F5" s="1" t="s">
         <v>96</v>
       </c>
@@ -2686,15 +2902,21 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="187" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" ht="153" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>37</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>147</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>96</v>
@@ -2721,15 +2943,21 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="272" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" ht="221" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>37</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>147</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>96</v>
@@ -2758,14 +2986,20 @@
     </row>
     <row r="8" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="D8" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F8" s="1" t="s">
         <v>96</v>
       </c>
@@ -2793,13 +3027,19 @@
     </row>
     <row r="9" spans="1:14" ht="153" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>37</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>152</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>96</v>
@@ -2828,13 +3068,19 @@
     </row>
     <row r="10" spans="1:14" ht="170" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>37</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>147</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>96</v>
@@ -2863,13 +3109,19 @@
     </row>
     <row r="11" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>37</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>147</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>96</v>
@@ -2898,14 +3150,20 @@
     </row>
     <row r="12" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="D12" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F12" s="1" t="s">
         <v>96</v>
       </c>
@@ -2933,13 +3191,19 @@
     </row>
     <row r="13" spans="1:14" ht="272" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>37</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>147</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>96</v>
@@ -2968,16 +3232,19 @@
     </row>
     <row r="14" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>147</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>96</v>
@@ -3065,7 +3332,7 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>94</v>
@@ -3084,6 +3351,12 @@
       <c r="C2" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F2" s="1" t="s">
         <v>98</v>
       </c>
@@ -3119,6 +3392,12 @@
       <c r="C3" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F3" s="1" t="s">
         <v>98</v>
       </c>
@@ -3154,6 +3433,12 @@
       <c r="C4" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D4" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F4" s="1" t="s">
         <v>98</v>
       </c>
@@ -3189,6 +3474,12 @@
       <c r="C5" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D5" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>152</v>
+      </c>
       <c r="F5" s="1" t="s">
         <v>98</v>
       </c>
@@ -3224,6 +3515,12 @@
       <c r="C6" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D6" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>152</v>
+      </c>
       <c r="F6" s="1" t="s">
         <v>98</v>
       </c>
@@ -3259,6 +3556,12 @@
       <c r="C7" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="D7" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F7" s="1" t="s">
         <v>98</v>
       </c>
@@ -3294,6 +3597,12 @@
       <c r="C8" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D8" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>152</v>
+      </c>
       <c r="F8" s="1" t="s">
         <v>98</v>
       </c>
@@ -3329,6 +3638,12 @@
       <c r="C9" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D9" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F9" s="1" t="s">
         <v>98</v>
       </c>
@@ -3364,6 +3679,12 @@
       <c r="C10" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D10" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F10" s="1" t="s">
         <v>98</v>
       </c>
@@ -3399,6 +3720,12 @@
       <c r="C11" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D11" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>152</v>
+      </c>
       <c r="F11" s="1" t="s">
         <v>98</v>
       </c>
@@ -3434,6 +3761,12 @@
       <c r="C12" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="D12" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F12" s="1" t="s">
         <v>98</v>
       </c>
@@ -3469,6 +3802,12 @@
       <c r="C13" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D13" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F13" s="1" t="s">
         <v>98</v>
       </c>
@@ -3504,6 +3843,12 @@
       <c r="C14" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D14" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>152</v>
+      </c>
       <c r="F14" s="1" t="s">
         <v>98</v>
       </c>
@@ -3539,6 +3884,12 @@
       <c r="C15" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="D15" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F15" s="1" t="s">
         <v>98</v>
       </c>
@@ -3574,6 +3925,12 @@
       <c r="C16" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D16" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>152</v>
+      </c>
       <c r="F16" s="1" t="s">
         <v>98</v>
       </c>
@@ -3609,6 +3966,12 @@
       <c r="C17" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D17" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F17" s="1" t="s">
         <v>98</v>
       </c>
@@ -3644,6 +4007,12 @@
       <c r="C18" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D18" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>152</v>
+      </c>
       <c r="F18" s="1" t="s">
         <v>98</v>
       </c>
@@ -3679,6 +4048,12 @@
       <c r="C19" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="D19" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>156</v>
+      </c>
       <c r="F19" s="1" t="s">
         <v>98</v>
       </c>
@@ -3741,16 +4116,19 @@
     </row>
     <row r="21" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>147</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>98</v>
